--- a/unitydata/excel/fabao.xlsx
+++ b/unitydata/excel/fabao.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
@@ -8,11 +8,12 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="combat_artifact" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <ns3:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -866,8 +867,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" ns1:Ignorable="x14ac x16r2">
+  <fonts count="7" ns2:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -973,11 +974,11 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <ns4:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3497,4 +3498,2170 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="30" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="0" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" s="0" t="str">
+        <v>family</v>
+      </c>
+      <c r="C1" s="0" t="str">
+        <v>quality</v>
+      </c>
+      <c r="D1" s="0" t="str">
+        <v>exclusive_group</v>
+      </c>
+      <c r="E1" s="0" t="str">
+        <v>selection_rank</v>
+      </c>
+      <c r="F1" s="0" t="str">
+        <v>effect_group</v>
+      </c>
+      <c r="G1" s="0" t="str">
+        <v>value</v>
+      </c>
+      <c r="H1" s="0" t="str">
+        <v>enabled</v>
+      </c>
+      <c r="I1" s="0" t="str">
+        <v>status</v>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="0" t="str">
+        <v>CS</v>
+      </c>
+      <c r="B2" s="0" t="str">
+        <v>CS</v>
+      </c>
+      <c r="C2" s="0" t="str">
+        <v>CS</v>
+      </c>
+      <c r="D2" s="0" t="str">
+        <v>CS</v>
+      </c>
+      <c r="E2" s="0" t="str">
+        <v>CS</v>
+      </c>
+      <c r="F2" s="0" t="str">
+        <v>CS</v>
+      </c>
+      <c r="G2" s="0" t="str">
+        <v>CS</v>
+      </c>
+      <c r="H2" s="0" t="str">
+        <v>CS</v>
+      </c>
+      <c r="I2" s="0" t="str">
+        <v>CS</v>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="0" t="str">
+        <v>id</v>
+      </c>
+      <c r="B3" s="0" t="str">
+        <v>family</v>
+      </c>
+      <c r="C3" s="0" t="str">
+        <v>quality</v>
+      </c>
+      <c r="D3" s="0" t="str">
+        <v>exclusive_group</v>
+      </c>
+      <c r="E3" s="0" t="str">
+        <v>selection_rank</v>
+      </c>
+      <c r="F3" s="0" t="str">
+        <v>effect_group</v>
+      </c>
+      <c r="G3" s="0" t="str">
+        <v>value</v>
+      </c>
+      <c r="H3" s="0" t="str">
+        <v>enabled</v>
+      </c>
+      <c r="I3" s="0" t="str">
+        <v>status</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="0" t="str">
+        <v>number</v>
+      </c>
+      <c r="B4" s="0" t="str">
+        <v>number</v>
+      </c>
+      <c r="C4" s="0" t="str">
+        <v>number</v>
+      </c>
+      <c r="D4" s="0" t="str">
+        <v>string</v>
+      </c>
+      <c r="E4" s="0" t="str">
+        <v>number</v>
+      </c>
+      <c r="F4" s="0" t="str">
+        <v>number</v>
+      </c>
+      <c r="G4" s="0" t="str">
+        <v>number</v>
+      </c>
+      <c r="H4" s="0" t="str">
+        <v>number</v>
+      </c>
+      <c r="I4" s="0" t="str">
+        <v>string</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="0" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>20001</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>400</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="0" t="n">
+        <v>1002</v>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>20002</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>400</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="0" t="n">
+        <v>1003</v>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>20003</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>800</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="0" t="n">
+        <v>1004</v>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>20004</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="0" t="n">
+        <v>1005</v>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>20005</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>400</v>
+      </c>
+      <c r="H9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="0" t="n">
+        <v>1006</v>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <v>20006</v>
+      </c>
+      <c r="G10" s="0" t="n">
+        <v>400</v>
+      </c>
+      <c r="H10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="0" t="n">
+        <v>1007</v>
+      </c>
+      <c r="B11" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="0" t="n">
+        <v>20007</v>
+      </c>
+      <c r="G11" s="0" t="n">
+        <v>800</v>
+      </c>
+      <c r="H11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="0" t="n">
+        <v>1008</v>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E12" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="0" t="n">
+        <v>20008</v>
+      </c>
+      <c r="G12" s="0" t="n">
+        <v>400</v>
+      </c>
+      <c r="H12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="0" t="n">
+        <v>1009</v>
+      </c>
+      <c r="B13" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E13" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="0" t="n">
+        <v>20009</v>
+      </c>
+      <c r="G13" s="0" t="n">
+        <v>400</v>
+      </c>
+      <c r="H13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="0" t="n">
+        <v>1010</v>
+      </c>
+      <c r="B14" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E14" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="0" t="n">
+        <v>20010</v>
+      </c>
+      <c r="G14" s="0" t="n">
+        <v>600</v>
+      </c>
+      <c r="H14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="0" t="n">
+        <v>1011</v>
+      </c>
+      <c r="B15" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="C15" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E15" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="0" t="n">
+        <v>20011</v>
+      </c>
+      <c r="G15" s="0" t="n">
+        <v>400</v>
+      </c>
+      <c r="H15" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="0" t="n">
+        <v>1012</v>
+      </c>
+      <c r="B16" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E16" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="0" t="n">
+        <v>20012</v>
+      </c>
+      <c r="G16" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H16" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="0" t="n">
+        <v>1013</v>
+      </c>
+      <c r="B17" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E17" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" s="0" t="n">
+        <v>20013</v>
+      </c>
+      <c r="G17" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="0" t="n">
+        <v>1014</v>
+      </c>
+      <c r="B18" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E18" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="0" t="n">
+        <v>20014</v>
+      </c>
+      <c r="G18" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H18" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="0" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B19" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E19" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" s="0" t="n">
+        <v>20001</v>
+      </c>
+      <c r="G19" s="0" t="n">
+        <v>600</v>
+      </c>
+      <c r="H19" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="0" t="n">
+        <v>1102</v>
+      </c>
+      <c r="B20" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E20" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" s="0" t="n">
+        <v>20002</v>
+      </c>
+      <c r="G20" s="0" t="n">
+        <v>600</v>
+      </c>
+      <c r="H20" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="0" t="n">
+        <v>1103</v>
+      </c>
+      <c r="B21" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E21" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" s="0" t="n">
+        <v>20003</v>
+      </c>
+      <c r="G21" s="0" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="0" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B22" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E22" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" s="0" t="n">
+        <v>20004</v>
+      </c>
+      <c r="G22" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H22" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="0" t="n">
+        <v>1105</v>
+      </c>
+      <c r="B23" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E23" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" s="0" t="n">
+        <v>20005</v>
+      </c>
+      <c r="G23" s="0" t="n">
+        <v>600</v>
+      </c>
+      <c r="H23" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="0" t="n">
+        <v>1106</v>
+      </c>
+      <c r="B24" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C24" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E24" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="0" t="n">
+        <v>20006</v>
+      </c>
+      <c r="G24" s="0" t="n">
+        <v>600</v>
+      </c>
+      <c r="H24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="0" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B25" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="C25" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E25" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" s="0" t="n">
+        <v>20007</v>
+      </c>
+      <c r="G25" s="0" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H25" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="0" t="n">
+        <v>1108</v>
+      </c>
+      <c r="B26" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="C26" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E26" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" s="0" t="n">
+        <v>20008</v>
+      </c>
+      <c r="G26" s="0" t="n">
+        <v>600</v>
+      </c>
+      <c r="H26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="0" t="n">
+        <v>1109</v>
+      </c>
+      <c r="B27" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="C27" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E27" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" s="0" t="n">
+        <v>20009</v>
+      </c>
+      <c r="G27" s="0" t="n">
+        <v>600</v>
+      </c>
+      <c r="H27" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="0" t="n">
+        <v>1110</v>
+      </c>
+      <c r="B28" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C28" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E28" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" s="0" t="n">
+        <v>20010</v>
+      </c>
+      <c r="G28" s="0" t="n">
+        <v>900</v>
+      </c>
+      <c r="H28" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="0" t="n">
+        <v>1111</v>
+      </c>
+      <c r="B29" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="C29" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E29" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" s="0" t="n">
+        <v>20011</v>
+      </c>
+      <c r="G29" s="0" t="n">
+        <v>600</v>
+      </c>
+      <c r="H29" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="0" t="n">
+        <v>1112</v>
+      </c>
+      <c r="B30" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C30" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E30" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" s="0" t="n">
+        <v>20012</v>
+      </c>
+      <c r="G30" s="0" t="n">
+        <v>2200</v>
+      </c>
+      <c r="H30" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="0" t="n">
+        <v>1113</v>
+      </c>
+      <c r="B31" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="C31" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E31" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" s="0" t="n">
+        <v>20013</v>
+      </c>
+      <c r="G31" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="0" t="n">
+        <v>1114</v>
+      </c>
+      <c r="B32" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C32" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E32" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" s="0" t="n">
+        <v>20014</v>
+      </c>
+      <c r="G32" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="H32" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="0" t="n">
+        <v>1201</v>
+      </c>
+      <c r="B33" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D33" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E33" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" s="0" t="n">
+        <v>20001</v>
+      </c>
+      <c r="G33" s="0" t="n">
+        <v>800</v>
+      </c>
+      <c r="H33" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="0" t="n">
+        <v>1202</v>
+      </c>
+      <c r="B34" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E34" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" s="0" t="n">
+        <v>20002</v>
+      </c>
+      <c r="G34" s="0" t="n">
+        <v>800</v>
+      </c>
+      <c r="H34" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="0" t="n">
+        <v>1203</v>
+      </c>
+      <c r="B35" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E35" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" s="0" t="n">
+        <v>20003</v>
+      </c>
+      <c r="G35" s="0" t="n">
+        <v>1600</v>
+      </c>
+      <c r="H35" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="0" t="n">
+        <v>1204</v>
+      </c>
+      <c r="B36" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E36" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" s="0" t="n">
+        <v>20004</v>
+      </c>
+      <c r="G36" s="0" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H36" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="0" t="n">
+        <v>1205</v>
+      </c>
+      <c r="B37" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C37" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E37" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" s="0" t="n">
+        <v>20005</v>
+      </c>
+      <c r="G37" s="0" t="n">
+        <v>800</v>
+      </c>
+      <c r="H37" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="0" t="n">
+        <v>1206</v>
+      </c>
+      <c r="B38" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C38" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D38" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E38" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F38" s="0" t="n">
+        <v>20006</v>
+      </c>
+      <c r="G38" s="0" t="n">
+        <v>800</v>
+      </c>
+      <c r="H38" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="0" t="n">
+        <v>1207</v>
+      </c>
+      <c r="B39" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="C39" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D39" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E39" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F39" s="0" t="n">
+        <v>20007</v>
+      </c>
+      <c r="G39" s="0" t="n">
+        <v>1600</v>
+      </c>
+      <c r="H39" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="0" t="n">
+        <v>1208</v>
+      </c>
+      <c r="B40" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="C40" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D40" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E40" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F40" s="0" t="n">
+        <v>20008</v>
+      </c>
+      <c r="G40" s="0" t="n">
+        <v>800</v>
+      </c>
+      <c r="H40" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="0" t="n">
+        <v>1209</v>
+      </c>
+      <c r="B41" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="C41" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E41" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F41" s="0" t="n">
+        <v>20009</v>
+      </c>
+      <c r="G41" s="0" t="n">
+        <v>800</v>
+      </c>
+      <c r="H41" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="0" t="n">
+        <v>1210</v>
+      </c>
+      <c r="B42" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C42" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D42" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E42" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F42" s="0" t="n">
+        <v>20010</v>
+      </c>
+      <c r="G42" s="0" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H42" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="0" t="n">
+        <v>1211</v>
+      </c>
+      <c r="B43" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="C43" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E43" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F43" s="0" t="n">
+        <v>20011</v>
+      </c>
+      <c r="G43" s="0" t="n">
+        <v>800</v>
+      </c>
+      <c r="H43" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="0" t="n">
+        <v>1212</v>
+      </c>
+      <c r="B44" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C44" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E44" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F44" s="0" t="n">
+        <v>20012</v>
+      </c>
+      <c r="G44" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H44" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="0" t="n">
+        <v>1213</v>
+      </c>
+      <c r="B45" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="C45" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D45" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E45" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F45" s="0" t="n">
+        <v>20013</v>
+      </c>
+      <c r="G45" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H45" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="0" t="n">
+        <v>1214</v>
+      </c>
+      <c r="B46" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C46" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D46" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E46" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" s="0" t="n">
+        <v>20014</v>
+      </c>
+      <c r="G46" s="0" t="n">
+        <v>400</v>
+      </c>
+      <c r="H46" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="0" t="n">
+        <v>1301</v>
+      </c>
+      <c r="B47" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D47" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E47" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F47" s="0" t="n">
+        <v>20001</v>
+      </c>
+      <c r="G47" s="0" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H47" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="0" t="n">
+        <v>1302</v>
+      </c>
+      <c r="B48" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D48" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E48" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F48" s="0" t="n">
+        <v>20002</v>
+      </c>
+      <c r="G48" s="0" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H48" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="0" t="n">
+        <v>1303</v>
+      </c>
+      <c r="B49" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C49" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D49" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E49" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F49" s="0" t="n">
+        <v>20003</v>
+      </c>
+      <c r="G49" s="0" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H49" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="0" t="n">
+        <v>1304</v>
+      </c>
+      <c r="B50" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C50" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D50" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E50" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F50" s="0" t="n">
+        <v>20004</v>
+      </c>
+      <c r="G50" s="0" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H50" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="0" t="n">
+        <v>1305</v>
+      </c>
+      <c r="B51" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C51" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D51" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E51" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F51" s="0" t="n">
+        <v>20005</v>
+      </c>
+      <c r="G51" s="0" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H51" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" s="0" t="n">
+        <v>1306</v>
+      </c>
+      <c r="B52" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C52" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D52" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E52" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F52" s="0" t="n">
+        <v>20006</v>
+      </c>
+      <c r="G52" s="0" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H52" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" s="0" t="n">
+        <v>1307</v>
+      </c>
+      <c r="B53" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="C53" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D53" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E53" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F53" s="0" t="n">
+        <v>20007</v>
+      </c>
+      <c r="G53" s="0" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H53" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="54" ht="24" customHeight="1">
+      <c r="A54" s="0" t="n">
+        <v>1308</v>
+      </c>
+      <c r="B54" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="C54" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D54" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E54" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F54" s="0" t="n">
+        <v>20008</v>
+      </c>
+      <c r="G54" s="0" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H54" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="A55" s="0" t="n">
+        <v>1309</v>
+      </c>
+      <c r="B55" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="C55" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D55" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E55" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F55" s="0" t="n">
+        <v>20009</v>
+      </c>
+      <c r="G55" s="0" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H55" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" s="0" t="n">
+        <v>1310</v>
+      </c>
+      <c r="B56" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C56" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D56" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E56" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F56" s="0" t="n">
+        <v>20010</v>
+      </c>
+      <c r="G56" s="0" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H56" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" s="0" t="n">
+        <v>1311</v>
+      </c>
+      <c r="B57" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="C57" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D57" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E57" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F57" s="0" t="n">
+        <v>20011</v>
+      </c>
+      <c r="G57" s="0" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H57" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="0" t="n">
+        <v>1312</v>
+      </c>
+      <c r="B58" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C58" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D58" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E58" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F58" s="0" t="n">
+        <v>20012</v>
+      </c>
+      <c r="G58" s="0" t="n">
+        <v>3700</v>
+      </c>
+      <c r="H58" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="59" ht="24" customHeight="1">
+      <c r="A59" s="0" t="n">
+        <v>1313</v>
+      </c>
+      <c r="B59" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="C59" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D59" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E59" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F59" s="0" t="n">
+        <v>20013</v>
+      </c>
+      <c r="G59" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="H59" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="60" ht="24" customHeight="1">
+      <c r="A60" s="0" t="n">
+        <v>1314</v>
+      </c>
+      <c r="B60" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C60" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D60" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E60" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F60" s="0" t="n">
+        <v>20014</v>
+      </c>
+      <c r="G60" s="0" t="n">
+        <v>500</v>
+      </c>
+      <c r="H60" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="61" ht="24" customHeight="1">
+      <c r="A61" s="0" t="n">
+        <v>1401</v>
+      </c>
+      <c r="B61" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="D61" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E61" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F61" s="0" t="n">
+        <v>20001</v>
+      </c>
+      <c r="G61" s="0" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H61" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="62" ht="24" customHeight="1">
+      <c r="A62" s="0" t="n">
+        <v>1402</v>
+      </c>
+      <c r="B62" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C62" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="D62" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E62" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F62" s="0" t="n">
+        <v>20002</v>
+      </c>
+      <c r="G62" s="0" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H62" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="0" t="n">
+        <v>1403</v>
+      </c>
+      <c r="B63" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="D63" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E63" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F63" s="0" t="n">
+        <v>20003</v>
+      </c>
+      <c r="G63" s="0" t="n">
+        <v>2400</v>
+      </c>
+      <c r="H63" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="64" ht="24" customHeight="1">
+      <c r="A64" s="0" t="n">
+        <v>1404</v>
+      </c>
+      <c r="B64" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C64" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="D64" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E64" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F64" s="0" t="n">
+        <v>20004</v>
+      </c>
+      <c r="G64" s="0" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H64" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="65" ht="24" customHeight="1">
+      <c r="A65" s="0" t="n">
+        <v>1405</v>
+      </c>
+      <c r="B65" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C65" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="D65" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E65" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F65" s="0" t="n">
+        <v>20005</v>
+      </c>
+      <c r="G65" s="0" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H65" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="66" ht="24" customHeight="1">
+      <c r="A66" s="0" t="n">
+        <v>1406</v>
+      </c>
+      <c r="B66" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="C66" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="D66" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E66" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F66" s="0" t="n">
+        <v>20006</v>
+      </c>
+      <c r="G66" s="0" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H66" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="67" ht="24" customHeight="1">
+      <c r="A67" s="0" t="n">
+        <v>1407</v>
+      </c>
+      <c r="B67" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="C67" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="D67" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E67" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F67" s="0" t="n">
+        <v>20007</v>
+      </c>
+      <c r="G67" s="0" t="n">
+        <v>2400</v>
+      </c>
+      <c r="H67" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="68" ht="24" customHeight="1">
+      <c r="A68" s="0" t="n">
+        <v>1408</v>
+      </c>
+      <c r="B68" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="C68" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="D68" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E68" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F68" s="0" t="n">
+        <v>20008</v>
+      </c>
+      <c r="G68" s="0" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H68" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="69" ht="24" customHeight="1">
+      <c r="A69" s="0" t="n">
+        <v>1409</v>
+      </c>
+      <c r="B69" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="C69" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="D69" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E69" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F69" s="0" t="n">
+        <v>20009</v>
+      </c>
+      <c r="G69" s="0" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H69" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="70" ht="24" customHeight="1">
+      <c r="A70" s="0" t="n">
+        <v>1410</v>
+      </c>
+      <c r="B70" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C70" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="D70" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E70" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F70" s="0" t="n">
+        <v>20010</v>
+      </c>
+      <c r="G70" s="0" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H70" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="71" ht="24" customHeight="1">
+      <c r="A71" s="0" t="n">
+        <v>1411</v>
+      </c>
+      <c r="B71" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="C71" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="D71" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E71" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F71" s="0" t="n">
+        <v>20011</v>
+      </c>
+      <c r="G71" s="0" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H71" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="72" ht="24" customHeight="1">
+      <c r="A72" s="0" t="n">
+        <v>1412</v>
+      </c>
+      <c r="B72" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C72" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="D72" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E72" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F72" s="0" t="n">
+        <v>20012</v>
+      </c>
+      <c r="G72" s="0" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H72" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="73" ht="24" customHeight="1">
+      <c r="A73" s="0" t="n">
+        <v>1413</v>
+      </c>
+      <c r="B73" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="C73" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="D73" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E73" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F73" s="0" t="n">
+        <v>20013</v>
+      </c>
+      <c r="G73" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="H73" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+    <row r="74" ht="24" customHeight="1">
+      <c r="A74" s="0" t="n">
+        <v>1414</v>
+      </c>
+      <c r="B74" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C74" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="D74" s="0" t="str">
+        <v>artifact_mechanism</v>
+      </c>
+      <c r="E74" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F74" s="0" t="n">
+        <v>20014</v>
+      </c>
+      <c r="G74" s="0" t="n">
+        <v>600</v>
+      </c>
+      <c r="H74" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" s="0" t="str">
+        <v>complete</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>